--- a/data/out/variants/v2_with_calendar_lags/summary_v2_with_calendar_lags.xlsx
+++ b/data/out/variants/v2_with_calendar_lags/summary_v2_with_calendar_lags.xlsx
@@ -526,16 +526,16 @@
         <v>0.9466131143771507</v>
       </c>
       <c r="F2" t="n">
-        <v>47.14645024017118</v>
+        <v>47.14645024017107</v>
       </c>
       <c r="G2" t="n">
-        <v>13422.39165677229</v>
+        <v>13422.39165677228</v>
       </c>
       <c r="H2" t="n">
-        <v>115.8550458839506</v>
+        <v>115.8550458839505</v>
       </c>
       <c r="I2" t="n">
-        <v>11.71052852403264</v>
+        <v>11.71052852403258</v>
       </c>
       <c r="J2" t="n">
         <v>48168</v>
@@ -547,7 +547,7 @@
         <v>9634</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1277213096618652</v>
+        <v>0.07976627349853516</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -574,19 +574,19 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.9466104321704324</v>
+        <v>0.9466104161510159</v>
       </c>
       <c r="F3" t="n">
-        <v>47.15875553488042</v>
+        <v>47.15877953148728</v>
       </c>
       <c r="G3" t="n">
-        <v>13423.06601019555</v>
+        <v>13423.07003775548</v>
       </c>
       <c r="H3" t="n">
-        <v>115.8579561799514</v>
+        <v>115.8579735614061</v>
       </c>
       <c r="I3" t="n">
-        <v>11.71336674492891</v>
+        <v>11.71338299322705</v>
       </c>
       <c r="J3" t="n">
         <v>48168</v>
@@ -598,7 +598,7 @@
         <v>9634</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09070110321044922</v>
+        <v>0.06215572357177734</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -625,19 +625,19 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.946787725849532</v>
+        <v>0.9467793724287179</v>
       </c>
       <c r="F4" t="n">
-        <v>46.44327335907337</v>
+        <v>46.49094067307723</v>
       </c>
       <c r="G4" t="n">
-        <v>13378.49129542467</v>
+        <v>13380.59149071668</v>
       </c>
       <c r="H4" t="n">
-        <v>115.665428263698</v>
+        <v>115.6745066586267</v>
       </c>
       <c r="I4" t="n">
-        <v>11.338659629886</v>
+        <v>11.36109174258125</v>
       </c>
       <c r="J4" t="n">
         <v>48168</v>
@@ -649,7 +649,7 @@
         <v>9634</v>
       </c>
       <c r="M4" t="n">
-        <v>3.924332618713379</v>
+        <v>2.116154909133911</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9465001424218891</v>
+        <v>0.9464980368160195</v>
       </c>
       <c r="F5" t="n">
-        <v>47.57370417446892</v>
+        <v>47.5774298540987</v>
       </c>
       <c r="G5" t="n">
-        <v>13450.79477135859</v>
+        <v>13451.3241572991</v>
       </c>
       <c r="H5" t="n">
-        <v>115.9775614994495</v>
+        <v>115.9798437544175</v>
       </c>
       <c r="I5" t="n">
-        <v>11.78146114947932</v>
+        <v>11.78382879747668</v>
       </c>
       <c r="J5" t="n">
         <v>48168</v>
@@ -704,7 +704,7 @@
         <v>9634</v>
       </c>
       <c r="M5" t="n">
-        <v>50.80814838409424</v>
+        <v>18.3661572933197</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-38.84010920323778</v>
+        <v>-38.83876134707462</v>
       </c>
     </row>
     <row r="6">
@@ -737,19 +737,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8414632613956305</v>
+        <v>0.8414632613956304</v>
       </c>
       <c r="F6" t="n">
-        <v>74.49491854489355</v>
+        <v>74.49491854489361</v>
       </c>
       <c r="G6" t="n">
-        <v>39858.89367227723</v>
+        <v>39858.89367227726</v>
       </c>
       <c r="H6" t="n">
-        <v>199.6469225214284</v>
+        <v>199.6469225214285</v>
       </c>
       <c r="I6" t="n">
-        <v>11.67003922183372</v>
+        <v>11.67003922183371</v>
       </c>
       <c r="J6" t="n">
         <v>48168</v>
@@ -761,7 +761,7 @@
         <v>9634</v>
       </c>
       <c r="M6" t="n">
-        <v>10.43058514595032</v>
+        <v>3.645622730255127</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-73.65134443835814</v>
+        <v>-72.59139310516363</v>
       </c>
     </row>
     <row r="7">
@@ -790,23 +790,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'min_samples_split': 2, 'n_estimators': 500}</t>
+          <t>{'max_depth': 5, 'min_samples_split': 5, 'n_estimators': 500}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8156548920260405</v>
+        <v>0.8155735516000052</v>
       </c>
       <c r="F7" t="n">
-        <v>76.0919519179087</v>
+        <v>76.1182781448839</v>
       </c>
       <c r="G7" t="n">
-        <v>46347.5666424237</v>
+        <v>46368.01704036387</v>
       </c>
       <c r="H7" t="n">
-        <v>215.2848500067381</v>
+        <v>215.3323409067107</v>
       </c>
       <c r="I7" t="n">
-        <v>11.44936269254109</v>
+        <v>11.45128557733594</v>
       </c>
       <c r="J7" t="n">
         <v>48168</v>
@@ -818,7 +818,7 @@
         <v>9634</v>
       </c>
       <c r="M7" t="n">
-        <v>4211.898075342178</v>
+        <v>1625.407452583313</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-77.83457337099095</v>
+        <v>-78.20173457890742</v>
       </c>
     </row>
     <row r="8">
@@ -847,23 +847,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.01, 'max_depth': 3, 'n_estimators': 500}</t>
+          <t>{'learning_rate': 0.05, 'max_depth': 3, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6876746446814674</v>
+        <v>0.6523983499730203</v>
       </c>
       <c r="F8" t="n">
-        <v>94.60569147950194</v>
+        <v>100.118049341135</v>
       </c>
       <c r="G8" t="n">
-        <v>78524.0269125512</v>
+        <v>87393.10099792635</v>
       </c>
       <c r="H8" t="n">
-        <v>280.2213891060981</v>
+        <v>295.6232416403121</v>
       </c>
       <c r="I8" t="n">
-        <v>12.69448733903967</v>
+        <v>13.21741340493487</v>
       </c>
       <c r="J8" t="n">
         <v>48168</v>
@@ -875,7 +875,7 @@
         <v>9634</v>
       </c>
       <c r="M8" t="n">
-        <v>1486.812394380569</v>
+        <v>1035.767039299011</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-73.9752235960281</v>
+        <v>-72.84527852786577</v>
       </c>
     </row>
     <row r="9">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.2391485748688392</v>
+        <v>0.2352639067309839</v>
       </c>
       <c r="F9" t="n">
-        <v>211.4099918793891</v>
+        <v>212.498195903966</v>
       </c>
       <c r="G9" t="n">
-        <v>191291.2825233791</v>
+        <v>192267.9556631317</v>
       </c>
       <c r="H9" t="n">
-        <v>437.3685888622766</v>
+        <v>438.4837005672294</v>
       </c>
       <c r="I9" t="n">
-        <v>49.49832696161466</v>
+        <v>49.67607447376013</v>
       </c>
       <c r="J9" t="n">
         <v>48168</v>
@@ -932,7 +932,7 @@
         <v>9634</v>
       </c>
       <c r="M9" t="n">
-        <v>293.1275699138641</v>
+        <v>267.1531438827515</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-207.4388384392404</v>
+        <v>-207.5421010541031</v>
       </c>
     </row>
     <row r="10">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6121125145811083</v>
+        <v>0.6109988646362644</v>
       </c>
       <c r="F10" t="n">
-        <v>153.5750901568848</v>
+        <v>154.7386288146149</v>
       </c>
       <c r="G10" t="n">
-        <v>97521.66074704703</v>
+        <v>97801.65171400165</v>
       </c>
       <c r="H10" t="n">
-        <v>312.2845829480652</v>
+        <v>312.7325562105769</v>
       </c>
       <c r="I10" t="n">
-        <v>40.09501608732898</v>
+        <v>40.01459313849168</v>
       </c>
       <c r="J10" t="n">
         <v>48168</v>
@@ -989,7 +989,7 @@
         <v>9634</v>
       </c>
       <c r="M10" t="n">
-        <v>2.917867422103882</v>
+        <v>2.690951108932495</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-118.2226056324873</v>
+        <v>-118.3007019119992</v>
       </c>
     </row>
     <row r="11">
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 664, 'learning_rate': 0.0159650598116664, 'max_depth': 3, 'subsample': 0.7442580345506755, 'colsample_bytree': 0.758914313870002}</t>
+          <t>{'n_estimators': 927, 'learning_rate': 0.010000007346645473, 'max_depth': 3, 'subsample': 0.8941688836939845, 'colsample_bytree': 0.683059175849614}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8125380627226516</v>
+        <v>0.8129480187710437</v>
       </c>
       <c r="F11" t="n">
-        <v>78.52932403006938</v>
+        <v>78.48229036957986</v>
       </c>
       <c r="G11" t="n">
-        <v>47131.19174340702</v>
+        <v>47028.12166206804</v>
       </c>
       <c r="H11" t="n">
-        <v>217.0971942320006</v>
+        <v>216.8596819652469</v>
       </c>
       <c r="I11" t="n">
-        <v>12.06908167592708</v>
+        <v>12.01338744207937</v>
       </c>
       <c r="J11" t="n">
         <v>48168</v>
@@ -1046,7 +1046,7 @@
         <v>9634</v>
       </c>
       <c r="M11" t="n">
-        <v>153.9240386486053</v>
+        <v>170.9529650211334</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 493, 'learning_rate': 0.033361152906203465, 'num_leaves': 61, 'min_child_samples': 43}</t>
+          <t>{'n_estimators': 582, 'learning_rate': 0.012805559787366494, 'num_leaves': 113, 'min_child_samples': 40}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7894660140606022</v>
+        <v>0.7952824880977947</v>
       </c>
       <c r="F12" t="n">
-        <v>83.36725382045982</v>
+        <v>82.01953676540317</v>
       </c>
       <c r="G12" t="n">
-        <v>52931.90609213075</v>
+        <v>51469.54334746392</v>
       </c>
       <c r="H12" t="n">
-        <v>230.0693506143979</v>
+        <v>226.8690004109506</v>
       </c>
       <c r="I12" t="n">
-        <v>11.62900811866453</v>
+        <v>11.48496919504807</v>
       </c>
       <c r="J12" t="n">
         <v>48168</v>
@@ -1101,7 +1101,7 @@
         <v>9634</v>
       </c>
       <c r="M12" t="n">
-        <v>190.9690170288086</v>
+        <v>246.2646718025208</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 695, 'learning_rate': 0.015181579792460858, 'depth': 4}</t>
+          <t>{'iterations': 558, 'learning_rate': 0.056982685763266996, 'depth': 4}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8090247827960606</v>
+        <v>0.8124340516981561</v>
       </c>
       <c r="F13" t="n">
-        <v>80.41277403299783</v>
+        <v>79.67970279793121</v>
       </c>
       <c r="G13" t="n">
-        <v>48014.49142692325</v>
+        <v>47157.34192413236</v>
       </c>
       <c r="H13" t="n">
-        <v>219.1220925121957</v>
+        <v>217.1574127773039</v>
       </c>
       <c r="I13" t="n">
-        <v>12.49252201245877</v>
+        <v>12.34454035053959</v>
       </c>
       <c r="J13" t="n">
         <v>48168</v>
@@ -1156,7 +1156,7 @@
         <v>9634</v>
       </c>
       <c r="M13" t="n">
-        <v>193.8531663417816</v>
+        <v>154.6764640808105</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.7188422207562037</v>
+        <v>0.7412088481829802</v>
       </c>
       <c r="F14" t="n">
-        <v>92.04075636556352</v>
+        <v>91.87876533111893</v>
       </c>
       <c r="G14" t="n">
-        <v>70687.95615871967</v>
+        <v>65064.59697863657</v>
       </c>
       <c r="H14" t="n">
-        <v>265.8720672780796</v>
+        <v>255.0776293182853</v>
       </c>
       <c r="I14" t="n">
-        <v>12.1471166785977</v>
+        <v>13.93806765587419</v>
       </c>
       <c r="J14" t="n">
         <v>48168</v>
@@ -1211,7 +1211,7 @@
         <v>9634</v>
       </c>
       <c r="M14" t="n">
-        <v>612.789618730545</v>
+        <v>189.786155462265</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-70.6326990271024</v>
+        <v>-71.67947607443074</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>9634</v>
       </c>
       <c r="M15" t="n">
-        <v>76.50887393951416</v>
+        <v>20.85575294494629</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1301,19 +1301,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9423195311145407</v>
+        <v>0.9380099773231011</v>
       </c>
       <c r="F16" t="n">
-        <v>51.84623808123195</v>
+        <v>53.94540291370113</v>
       </c>
       <c r="G16" t="n">
-        <v>14501.87317155552</v>
+        <v>15585.36995507785</v>
       </c>
       <c r="H16" t="n">
-        <v>120.4237234582768</v>
+        <v>124.8413791780508</v>
       </c>
       <c r="I16" t="n">
-        <v>12.54938358981489</v>
+        <v>12.4165899101669</v>
       </c>
       <c r="J16" t="n">
         <v>48168</v>
@@ -1325,7 +1325,7 @@
         <v>9634</v>
       </c>
       <c r="M16" t="n">
-        <v>1317.301121473312</v>
+        <v>931.6854968070984</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-41.43159214955772</v>
+        <v>-40.88922316297074</v>
       </c>
     </row>
   </sheetData>
